--- a/output/yearly_total_coral_cover_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_28_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.271467769528168</v>
+        <v>1.253501786540451</v>
       </c>
       <c r="C3" t="n">
-        <v>4.703402934707881</v>
+        <v>4.597639254529371</v>
       </c>
       <c r="D3" t="n">
-        <v>6.139992589711308</v>
+        <v>6.073263198253652</v>
       </c>
       <c r="E3" t="n">
-        <v>12.11486329394736</v>
+        <v>11.92440423932347</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.430364796170445</v>
+        <v>1.387769951190357</v>
       </c>
       <c r="C4" t="n">
-        <v>5.348093600902128</v>
+        <v>5.02940264581095</v>
       </c>
       <c r="D4" t="n">
-        <v>6.384072313583708</v>
+        <v>6.369762272095591</v>
       </c>
       <c r="E4" t="n">
-        <v>13.16253071065628</v>
+        <v>12.7869348690969</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.640094078261132</v>
+        <v>1.583339822024948</v>
       </c>
       <c r="C5" t="n">
-        <v>6.208816764377135</v>
+        <v>5.567752175625731</v>
       </c>
       <c r="D5" t="n">
-        <v>6.673856017519318</v>
+        <v>6.724969025057542</v>
       </c>
       <c r="E5" t="n">
-        <v>14.52276686015759</v>
+        <v>13.87606102270822</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.883404218150913</v>
+        <v>1.811685513538933</v>
       </c>
       <c r="C6" t="n">
-        <v>7.249040174924721</v>
+        <v>6.24413829077972</v>
       </c>
       <c r="D6" t="n">
-        <v>7.089509369735493</v>
+        <v>7.120480925232533</v>
       </c>
       <c r="E6" t="n">
-        <v>16.22195376281113</v>
+        <v>15.17630472955119</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.153410362360539</v>
+        <v>2.059043478855308</v>
       </c>
       <c r="C7" t="n">
-        <v>8.441633208909201</v>
+        <v>7.019870166031149</v>
       </c>
       <c r="D7" t="n">
-        <v>7.471658245669772</v>
+        <v>7.5469421769833</v>
       </c>
       <c r="E7" t="n">
-        <v>18.06670181693951</v>
+        <v>16.62585582186976</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.372328954905545</v>
+        <v>1.282866602183306</v>
       </c>
       <c r="C8" t="n">
-        <v>6.096491209135353</v>
+        <v>4.686642562310999</v>
       </c>
       <c r="D8" t="n">
-        <v>5.762999410792742</v>
+        <v>5.852797317051524</v>
       </c>
       <c r="E8" t="n">
-        <v>13.23181957483364</v>
+        <v>11.82230648154583</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.744260848331738</v>
+        <v>1.612823844715113</v>
       </c>
       <c r="C9" t="n">
-        <v>7.634256605637801</v>
+        <v>5.67066762445029</v>
       </c>
       <c r="D9" t="n">
-        <v>6.239909508131491</v>
+        <v>6.527513121883854</v>
       </c>
       <c r="E9" t="n">
-        <v>15.61842696210103</v>
+        <v>13.81100459104926</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.114612538879455</v>
+        <v>1.956446272103114</v>
       </c>
       <c r="C10" t="n">
-        <v>9.415647468208922</v>
+        <v>6.830873216250103</v>
       </c>
       <c r="D10" t="n">
-        <v>6.795847394770612</v>
+        <v>7.168515381518303</v>
       </c>
       <c r="E10" t="n">
-        <v>18.32610740185899</v>
+        <v>15.95583486987152</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.46504230930455</v>
+        <v>2.307075012506864</v>
       </c>
       <c r="C11" t="n">
-        <v>11.31078180172105</v>
+        <v>8.128522037014314</v>
       </c>
       <c r="D11" t="n">
-        <v>7.299973038133328</v>
+        <v>7.827961122580048</v>
       </c>
       <c r="E11" t="n">
-        <v>21.07579714915893</v>
+        <v>18.26355817210123</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.804200166169093</v>
+        <v>2.66628868779223</v>
       </c>
       <c r="C12" t="n">
-        <v>13.22291354508967</v>
+        <v>9.512960058583275</v>
       </c>
       <c r="D12" t="n">
-        <v>7.74853867960599</v>
+        <v>8.512448846360471</v>
       </c>
       <c r="E12" t="n">
-        <v>23.77565239086476</v>
+        <v>20.69169759273598</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.104339078191048</v>
+        <v>3.01871555310146</v>
       </c>
       <c r="C13" t="n">
-        <v>15.13447396070672</v>
+        <v>10.93157094767474</v>
       </c>
       <c r="D13" t="n">
-        <v>8.136299676901556</v>
+        <v>9.212231122344733</v>
       </c>
       <c r="E13" t="n">
-        <v>26.37511271579933</v>
+        <v>23.16251762312094</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.761510635821882</v>
+        <v>1.749160249702457</v>
       </c>
       <c r="C14" t="n">
-        <v>10.45457239766203</v>
+        <v>7.707848488197345</v>
       </c>
       <c r="D14" t="n">
-        <v>6.175507218977796</v>
+        <v>7.017758391928177</v>
       </c>
       <c r="E14" t="n">
-        <v>18.39159025246171</v>
+        <v>16.47476712982798</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.782470949307551</v>
+        <v>1.795331844233185</v>
       </c>
       <c r="C15" t="n">
-        <v>11.36636076050421</v>
+        <v>8.283319539995698</v>
       </c>
       <c r="D15" t="n">
-        <v>6.157001274752743</v>
+        <v>7.16558014375662</v>
       </c>
       <c r="E15" t="n">
-        <v>19.30583298456451</v>
+        <v>17.24423152798551</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.050419350227633</v>
+        <v>2.087195619228719</v>
       </c>
       <c r="C16" t="n">
-        <v>13.38237967117504</v>
+        <v>9.750580753900726</v>
       </c>
       <c r="D16" t="n">
-        <v>6.524989766735576</v>
+        <v>7.840335340885453</v>
       </c>
       <c r="E16" t="n">
-        <v>21.95778878813825</v>
+        <v>19.6781117140149</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.635120436377148</v>
+        <v>1.677090150733699</v>
       </c>
       <c r="C17" t="n">
-        <v>12.22886538859321</v>
+        <v>8.989363036458876</v>
       </c>
       <c r="D17" t="n">
-        <v>6.007755988753145</v>
+        <v>7.390292375781672</v>
       </c>
       <c r="E17" t="n">
-        <v>19.8717418137235</v>
+        <v>18.05674556297425</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.846480899624444</v>
+        <v>1.921191899917626</v>
       </c>
       <c r="C18" t="n">
-        <v>14.16136702206375</v>
+        <v>10.40885240707525</v>
       </c>
       <c r="D18" t="n">
-        <v>6.373731897942269</v>
+        <v>7.975306015265303</v>
       </c>
       <c r="E18" t="n">
-        <v>22.38157981963046</v>
+        <v>20.30535032225819</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.834159965936146</v>
+        <v>1.93143152847292</v>
       </c>
       <c r="C19" t="n">
-        <v>15.03371857962634</v>
+        <v>11.07333852321767</v>
       </c>
       <c r="D19" t="n">
-        <v>6.40551107112874</v>
+        <v>8.183868497555496</v>
       </c>
       <c r="E19" t="n">
-        <v>23.27338961669123</v>
+        <v>21.18863854924608</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.02522770413666</v>
+        <v>2.160002028975663</v>
       </c>
       <c r="C20" t="n">
-        <v>17.15425435089129</v>
+        <v>12.64964245463339</v>
       </c>
       <c r="D20" t="n">
-        <v>6.747414526609733</v>
+        <v>8.768931224424341</v>
       </c>
       <c r="E20" t="n">
-        <v>25.92689658163768</v>
+        <v>23.57857570803339</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.192332586807751</v>
+        <v>1.29264756722769</v>
       </c>
       <c r="C21" t="n">
-        <v>12.46797985943956</v>
+        <v>9.252913207663934</v>
       </c>
       <c r="D21" t="n">
-        <v>5.604984175608847</v>
+        <v>7.401562839426426</v>
       </c>
       <c r="E21" t="n">
-        <v>19.26529662185616</v>
+        <v>17.94712361431805</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_28_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.253501786540451</v>
+        <v>1.26157175266936</v>
       </c>
       <c r="C3" t="n">
-        <v>4.597639254529371</v>
+        <v>4.620661238193959</v>
       </c>
       <c r="D3" t="n">
-        <v>6.073263198253652</v>
+        <v>6.169945712167878</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92440423932347</v>
+        <v>12.0521787030312</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.387769951190357</v>
+        <v>1.393334168690084</v>
       </c>
       <c r="C4" t="n">
-        <v>5.02940264581095</v>
+        <v>5.102879659754707</v>
       </c>
       <c r="D4" t="n">
-        <v>6.369762272095591</v>
+        <v>6.474571077361282</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7869348690969</v>
+        <v>12.97078490580607</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.583339822024948</v>
+        <v>1.568445516131346</v>
       </c>
       <c r="C5" t="n">
-        <v>5.567752175625731</v>
+        <v>5.704213616696645</v>
       </c>
       <c r="D5" t="n">
-        <v>6.724969025057542</v>
+        <v>6.821128377937678</v>
       </c>
       <c r="E5" t="n">
-        <v>13.87606102270822</v>
+        <v>14.09378751076567</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.811685513538933</v>
+        <v>1.766643265253646</v>
       </c>
       <c r="C6" t="n">
-        <v>6.24413829077972</v>
+        <v>6.465994707189604</v>
       </c>
       <c r="D6" t="n">
-        <v>7.120480925232533</v>
+        <v>7.306470279027717</v>
       </c>
       <c r="E6" t="n">
-        <v>15.17630472955119</v>
+        <v>15.53910825147097</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.059043478855308</v>
+        <v>2.006350805629005</v>
       </c>
       <c r="C7" t="n">
-        <v>7.019870166031149</v>
+        <v>7.356506904045966</v>
       </c>
       <c r="D7" t="n">
-        <v>7.5469421769833</v>
+        <v>7.774140068962108</v>
       </c>
       <c r="E7" t="n">
-        <v>16.62585582186976</v>
+        <v>17.13699777863708</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.282866602183306</v>
+        <v>1.241030639958449</v>
       </c>
       <c r="C8" t="n">
-        <v>4.686642562310999</v>
+        <v>5.015757270302001</v>
       </c>
       <c r="D8" t="n">
-        <v>5.852797317051524</v>
+        <v>6.053815559500787</v>
       </c>
       <c r="E8" t="n">
-        <v>11.82230648154583</v>
+        <v>12.31060346976124</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.612823844715113</v>
+        <v>1.566886170591382</v>
       </c>
       <c r="C9" t="n">
-        <v>5.67066762445029</v>
+        <v>6.134810493980153</v>
       </c>
       <c r="D9" t="n">
-        <v>6.527513121883854</v>
+        <v>6.694400504694206</v>
       </c>
       <c r="E9" t="n">
-        <v>13.81100459104926</v>
+        <v>14.39609716926574</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.956446272103114</v>
+        <v>1.904014608756598</v>
       </c>
       <c r="C10" t="n">
-        <v>6.830873216250103</v>
+        <v>7.382524535244939</v>
       </c>
       <c r="D10" t="n">
-        <v>7.168515381518303</v>
+        <v>7.346509310127645</v>
       </c>
       <c r="E10" t="n">
-        <v>15.95583486987152</v>
+        <v>16.63304845412918</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.307075012506864</v>
+        <v>2.253464864716366</v>
       </c>
       <c r="C11" t="n">
-        <v>8.128522037014314</v>
+        <v>8.779180042877462</v>
       </c>
       <c r="D11" t="n">
-        <v>7.827961122580048</v>
+        <v>7.916686314141133</v>
       </c>
       <c r="E11" t="n">
-        <v>18.26355817210123</v>
+        <v>18.94933122173496</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.66628868779223</v>
+        <v>2.613042907848023</v>
       </c>
       <c r="C12" t="n">
-        <v>9.512960058583275</v>
+        <v>10.2851222455024</v>
       </c>
       <c r="D12" t="n">
-        <v>8.512448846360471</v>
+        <v>8.602919264446399</v>
       </c>
       <c r="E12" t="n">
-        <v>20.69169759273598</v>
+        <v>21.50108441779683</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.01871555310146</v>
+        <v>2.952210375907209</v>
       </c>
       <c r="C13" t="n">
-        <v>10.93157094767474</v>
+        <v>11.81913553216489</v>
       </c>
       <c r="D13" t="n">
-        <v>9.212231122344733</v>
+        <v>9.125785219893556</v>
       </c>
       <c r="E13" t="n">
-        <v>23.16251762312094</v>
+        <v>23.89713112796566</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.749160249702457</v>
+        <v>1.695615729912836</v>
       </c>
       <c r="C14" t="n">
-        <v>7.707848488197345</v>
+        <v>8.343481039311943</v>
       </c>
       <c r="D14" t="n">
-        <v>7.017758391928177</v>
+        <v>6.898446593431063</v>
       </c>
       <c r="E14" t="n">
-        <v>16.47476712982798</v>
+        <v>16.93754336265584</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.795331844233185</v>
+        <v>1.745645592921253</v>
       </c>
       <c r="C15" t="n">
-        <v>8.283319539995698</v>
+        <v>9.051802190448974</v>
       </c>
       <c r="D15" t="n">
-        <v>7.16558014375662</v>
+        <v>6.977938705043927</v>
       </c>
       <c r="E15" t="n">
-        <v>17.24423152798551</v>
+        <v>17.77538648841416</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.087195619228719</v>
+        <v>2.037018494064665</v>
       </c>
       <c r="C16" t="n">
-        <v>9.750580753900726</v>
+        <v>10.70251278036956</v>
       </c>
       <c r="D16" t="n">
-        <v>7.840335340885453</v>
+        <v>7.506914185569151</v>
       </c>
       <c r="E16" t="n">
-        <v>19.6781117140149</v>
+        <v>20.24644546000338</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.677090150733699</v>
+        <v>1.64368127635818</v>
       </c>
       <c r="C17" t="n">
-        <v>8.989363036458876</v>
+        <v>9.901013954622464</v>
       </c>
       <c r="D17" t="n">
-        <v>7.390292375781672</v>
+        <v>7.006556650622722</v>
       </c>
       <c r="E17" t="n">
-        <v>18.05674556297425</v>
+        <v>18.55125188160337</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.921191899917626</v>
+        <v>1.876689276484118</v>
       </c>
       <c r="C18" t="n">
-        <v>10.40885240707525</v>
+        <v>11.57137913358207</v>
       </c>
       <c r="D18" t="n">
-        <v>7.975306015265303</v>
+        <v>7.50559864364546</v>
       </c>
       <c r="E18" t="n">
-        <v>20.30535032225819</v>
+        <v>20.95366705371165</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.93143152847292</v>
+        <v>1.881725642206904</v>
       </c>
       <c r="C19" t="n">
-        <v>11.07333852321767</v>
+        <v>12.40169225444881</v>
       </c>
       <c r="D19" t="n">
-        <v>8.183868497555496</v>
+        <v>7.634865363863637</v>
       </c>
       <c r="E19" t="n">
-        <v>21.18863854924608</v>
+        <v>21.91828326051935</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.160002028975663</v>
+        <v>2.085084861664589</v>
       </c>
       <c r="C20" t="n">
-        <v>12.64964245463339</v>
+        <v>14.2437454719271</v>
       </c>
       <c r="D20" t="n">
-        <v>8.768931224424341</v>
+        <v>8.080500281775352</v>
       </c>
       <c r="E20" t="n">
-        <v>23.57857570803339</v>
+        <v>24.40933061536704</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.29264756722769</v>
+        <v>1.234822627447553</v>
       </c>
       <c r="C21" t="n">
-        <v>9.252913207663934</v>
+        <v>10.47067306001168</v>
       </c>
       <c r="D21" t="n">
-        <v>7.401562839426426</v>
+        <v>6.752136733067161</v>
       </c>
       <c r="E21" t="n">
-        <v>17.94712361431805</v>
+        <v>18.45763242052639</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_28_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26157175266936</v>
+        <v>2.606902923309383</v>
       </c>
       <c r="C3" t="n">
-        <v>4.620661238193959</v>
+        <v>7.691008684426018</v>
       </c>
       <c r="D3" t="n">
-        <v>6.169945712167878</v>
+        <v>8.17631666276726</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0521787030312</v>
+        <v>18.47422827050266</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.393334168690084</v>
+        <v>1.097380667675094</v>
       </c>
       <c r="C4" t="n">
-        <v>5.102879659754707</v>
+        <v>4.452121985654861</v>
       </c>
       <c r="D4" t="n">
-        <v>6.474571077361282</v>
+        <v>5.769260200215273</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97078490580607</v>
+        <v>11.31876285354523</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.568445516131346</v>
+        <v>1.218076199604957</v>
       </c>
       <c r="C5" t="n">
-        <v>5.704213616696645</v>
+        <v>5.040427561712576</v>
       </c>
       <c r="D5" t="n">
-        <v>6.821128377937678</v>
+        <v>6.061715987482603</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09378751076567</v>
+        <v>12.32021974880014</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.766643265253646</v>
+        <v>1.359210620249886</v>
       </c>
       <c r="C6" t="n">
-        <v>6.465994707189604</v>
+        <v>5.787015489085469</v>
       </c>
       <c r="D6" t="n">
-        <v>7.306470279027717</v>
+        <v>6.357853858184628</v>
       </c>
       <c r="E6" t="n">
-        <v>15.53910825147097</v>
+        <v>13.50407996751998</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.006350805629005</v>
+        <v>1.505850500500866</v>
       </c>
       <c r="C7" t="n">
-        <v>7.356506904045966</v>
+        <v>6.672940021428</v>
       </c>
       <c r="D7" t="n">
-        <v>7.774140068962108</v>
+        <v>6.788186865205085</v>
       </c>
       <c r="E7" t="n">
-        <v>17.13699777863708</v>
+        <v>14.96697738713395</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.241030639958449</v>
+        <v>1.653563192802998</v>
       </c>
       <c r="C8" t="n">
-        <v>5.015757270302001</v>
+        <v>7.664144505673969</v>
       </c>
       <c r="D8" t="n">
-        <v>6.053815559500787</v>
+        <v>7.316800126276779</v>
       </c>
       <c r="E8" t="n">
-        <v>12.31060346976124</v>
+        <v>16.63450782475375</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.566886170591382</v>
+        <v>1.806031424996521</v>
       </c>
       <c r="C9" t="n">
-        <v>6.134810493980153</v>
+        <v>8.754433288737461</v>
       </c>
       <c r="D9" t="n">
-        <v>6.694400504694206</v>
+        <v>7.835368680223554</v>
       </c>
       <c r="E9" t="n">
-        <v>14.39609716926574</v>
+        <v>18.39583339395753</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.904014608756598</v>
+        <v>1.11651221160877</v>
       </c>
       <c r="C10" t="n">
-        <v>7.382524535244939</v>
+        <v>6.480359516100515</v>
       </c>
       <c r="D10" t="n">
-        <v>7.346509310127645</v>
+        <v>6.209603316746288</v>
       </c>
       <c r="E10" t="n">
-        <v>16.63304845412918</v>
+        <v>13.80647504445557</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.253464864716366</v>
+        <v>1.063537105487612</v>
       </c>
       <c r="C11" t="n">
-        <v>8.779180042877462</v>
+        <v>6.736556397000763</v>
       </c>
       <c r="D11" t="n">
-        <v>7.916686314141133</v>
+        <v>6.144778515834871</v>
       </c>
       <c r="E11" t="n">
-        <v>18.94933122173496</v>
+        <v>13.94487201832325</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.613042907848023</v>
+        <v>1.161005017565235</v>
       </c>
       <c r="C12" t="n">
-        <v>10.2851222455024</v>
+        <v>7.847884980731111</v>
       </c>
       <c r="D12" t="n">
-        <v>8.602919264446399</v>
+        <v>6.61247330466101</v>
       </c>
       <c r="E12" t="n">
-        <v>21.50108441779683</v>
+        <v>15.62136330295736</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.952210375907209</v>
+        <v>0.923706779971739</v>
       </c>
       <c r="C13" t="n">
-        <v>11.81913553216489</v>
+        <v>7.381083582315837</v>
       </c>
       <c r="D13" t="n">
-        <v>9.125785219893556</v>
+        <v>6.122522295379595</v>
       </c>
       <c r="E13" t="n">
-        <v>23.89713112796566</v>
+        <v>14.42731265766717</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.695615729912836</v>
+        <v>1.009570434185165</v>
       </c>
       <c r="C14" t="n">
-        <v>8.343481039311943</v>
+        <v>8.541538821166695</v>
       </c>
       <c r="D14" t="n">
-        <v>6.898446593431063</v>
+        <v>6.608035805037814</v>
       </c>
       <c r="E14" t="n">
-        <v>16.93754336265584</v>
+        <v>16.15914506038968</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.745645592921253</v>
+        <v>0.9861753863929636</v>
       </c>
       <c r="C15" t="n">
-        <v>9.051802190448974</v>
+        <v>9.114319884255412</v>
       </c>
       <c r="D15" t="n">
-        <v>6.977938705043927</v>
+        <v>6.75046776196994</v>
       </c>
       <c r="E15" t="n">
-        <v>17.77538648841416</v>
+        <v>16.85096303261832</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.037018494064665</v>
+        <v>1.082003779804495</v>
       </c>
       <c r="C16" t="n">
-        <v>10.70251278036956</v>
+        <v>10.59788792752798</v>
       </c>
       <c r="D16" t="n">
-        <v>7.506914185569151</v>
+        <v>7.269684670314951</v>
       </c>
       <c r="E16" t="n">
-        <v>20.24644546000338</v>
+        <v>18.94957637764742</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.64368127635818</v>
+        <v>0.6502900443390025</v>
       </c>
       <c r="C17" t="n">
-        <v>9.901013954622464</v>
+        <v>7.969621696057716</v>
       </c>
       <c r="D17" t="n">
-        <v>7.006556650622722</v>
+        <v>6.117299397593002</v>
       </c>
       <c r="E17" t="n">
-        <v>18.55125188160337</v>
+        <v>14.73721113798972</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.876689276484118</v>
+        <v>0.5074948407563037</v>
       </c>
       <c r="C18" t="n">
-        <v>11.57137913358207</v>
+        <v>6.953836798904669</v>
       </c>
       <c r="D18" t="n">
-        <v>7.50559864364546</v>
+        <v>5.681521226631929</v>
       </c>
       <c r="E18" t="n">
-        <v>20.95366705371165</v>
+        <v>13.1428528662929</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.881725642206904</v>
+        <v>0.5947329417556754</v>
       </c>
       <c r="C19" t="n">
-        <v>12.40169225444881</v>
+        <v>8.573533978848097</v>
       </c>
       <c r="D19" t="n">
-        <v>7.634865363863637</v>
+        <v>6.281977757503363</v>
       </c>
       <c r="E19" t="n">
-        <v>21.91828326051935</v>
+        <v>15.45024467810713</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.085084861664589</v>
+        <v>0.6783778461575035</v>
       </c>
       <c r="C20" t="n">
-        <v>14.2437454719271</v>
+        <v>10.30412937946325</v>
       </c>
       <c r="D20" t="n">
-        <v>8.080500281775352</v>
+        <v>6.891093303126254</v>
       </c>
       <c r="E20" t="n">
-        <v>24.40933061536704</v>
+        <v>17.87360052874701</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.234822627447553</v>
+        <v>0.7512333432896594</v>
       </c>
       <c r="C21" t="n">
-        <v>10.47067306001168</v>
+        <v>12.03226059334074</v>
       </c>
       <c r="D21" t="n">
-        <v>6.752136733067161</v>
+        <v>7.506727653505345</v>
       </c>
       <c r="E21" t="n">
-        <v>18.45763242052639</v>
+        <v>20.29022159013574</v>
       </c>
     </row>
   </sheetData>
